--- a/engine/sc/qa/unit/data/xlsx/pivot-table/PivotTableCellFormatsTest_12_WholeLabelColumnSelected.xlsx
+++ b/engine/sc/qa/unit/data/xlsx/pivot-table/PivotTableCellFormatsTest_12_WholeLabelColumnSelected.xlsx
@@ -1,39 +1,56 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\VBOXSVR\quikee\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44CC7DD-160E-477B-AA3F-AB4226AD2317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{B44CC7DD-160E-477B-AA3F-AB4226AD2317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BD47C0A-AA7A-4782-93BF-C83166A7EDED}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="27288" windowHeight="16224" xr2:uid="{D77C3CC8-6808-493C-9198-7EE457FDC5AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId2"/>
+    <pivotCache cacheId="266" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="11">
   <si>
     <t>A</t>
   </si>
   <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Sum of B</t>
   </si>
   <si>
     <t>a</t>
@@ -54,20 +71,14 @@
     <t>f</t>
   </si>
   <si>
-    <t>Row Labels</t>
-  </si>
-  <si>
     <t>Grand Total</t>
-  </si>
-  <si>
-    <t>Sum of B</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,7 +101,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -98,19 +109,103 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" pivotButton="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -134,72 +229,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6C8FC5D-58F5-39DF-75C9-4849492796CD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3048000" y="1828800"/>
-          <a:ext cx="1455420" cy="1470660"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -356,7 +385,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6B5158F5-F24C-4290-B1AB-DF7060F272DC}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6B5158F5-F24C-4290-B1AB-DF7060F272DC}" name="PivotTable1" cacheId="266" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="F1:G8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" showAll="0">
@@ -413,7 +442,7 @@
       </pivotArea>
     </format>
   </formats>
-  <pivotTableStyleInfo name="PivotStyleLight15" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -723,13 +752,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E559A02-FAA2-4FD3-AB40-361DCD664D06}">
   <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="6" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -737,289 +766,337 @@
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2">
+      <c r="F2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3">
+      <c r="F3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4">
+      <c r="F4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="4">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5">
+      <c r="F5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
+      <c r="F6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="4">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8">
+      <c r="F8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="15">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B10">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F10" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F11" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F12" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F13" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F14" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F16" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B28">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B30">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -1027,6 +1104,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>